--- a/data/trans_orig/P25C$parches_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P25C$parches_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según método de dejar de fumar (multirrespuesta) en 2023</t>
+          <t>Población según método de dejar de fumar (multirrespuesta) en 2023 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9582</t>
+          <t>9586</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2563</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,62 +991,62 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1132</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>2819</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>2872</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>142731</t>
+          <t>142857</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155640</t>
+          <t>155553</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38660</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43525</t>
+          <t>43364</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>183453</t>
+          <t>183357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>197775</t>
+          <t>197515</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8773</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>400</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4513</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>10956</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>13031</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,39 +1423,39 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2962</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>1,38%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3223</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>13643</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9472</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>11076</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18414</t>
+          <t>17714</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>11342</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,62 +1786,62 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1771</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1258</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>7088</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1771</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>6671</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>555</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5188</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>10134</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>486898</t>
+          <t>485064</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>535688</t>
+          <t>535658</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>176272</t>
+          <t>175288</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>188888</t>
+          <t>188896</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>669482</t>
+          <t>670550</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>729465</t>
+          <t>728784</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>984</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16875</t>
+          <t>17537</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13158</t>
+          <t>13721</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23792</t>
+          <t>24026</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31016</t>
+          <t>32021</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12683</t>
+          <t>13244</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35751</t>
+          <t>37252</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>854</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>6694</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>929</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -2546,97 +2546,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1606</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1795</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>377</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2282</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>1925</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>2168</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>107831</t>
+          <t>108300</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125193</t>
+          <t>125838</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70524</t>
+          <t>70781</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80814</t>
+          <t>80472</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>183379</t>
+          <t>184693</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>203677</t>
+          <t>204120</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23721</t>
+          <t>23970</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5534</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25283</t>
+          <t>25456</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10025</t>
+          <t>10355</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11420</t>
+          <t>11127</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17998</t>
+          <t>18174</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15083</t>
+          <t>15113</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>8760</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28530</t>
+          <t>28087</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>813</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9860</t>
+          <t>9956</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10746</t>
+          <t>10676</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16628</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,82 +3356,82 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2318</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>2708</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
           <t>0,04%</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>1900</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>2708</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>7688</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>11287</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>16944</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>750334</t>
+          <t>751539</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>821221</t>
+          <t>821625</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>291676</t>
+          <t>291390</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>309013</t>
+          <t>309803</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1052750</t>
+          <t>1052678</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1132424</t>
+          <t>1129955</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>38542</t>
+          <t>40113</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>17747</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15990</t>
+          <t>14808</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>48987</t>
+          <t>50348</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -3793,12 +3793,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>39779</t>
+          <t>40548</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3808,12 +3808,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5627</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15428</t>
+          <t>15565</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>16803</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>48372</t>
+          <t>49768</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25C$parches_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P25C$parches_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2166</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9586</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>10596</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>609</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1613</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>571</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>571</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>669</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>646</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>149771</t>
+          <t>159165</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>142857</t>
+          <t>150690</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155553</t>
+          <t>165441</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>41632</t>
+          <t>44234</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38104</t>
+          <t>40862</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43364</t>
+          <t>46186</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>191403</t>
+          <t>203399</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>183357</t>
+          <t>195120</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>197515</t>
+          <t>209669</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>10242</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>407</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10956</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -1403,32 +1403,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>13409</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>670</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6768</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>945</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9937</t>
+          <t>8209</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,27 +1555,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>7015</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>12114</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>9965</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17714</t>
+          <t>17439</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>803</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2384</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11342</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7088</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2248</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>604</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10134</t>
+          <t>11697</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>515697</t>
+          <t>300741</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>485064</t>
+          <t>289364</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>535658</t>
+          <t>310777</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>183274</t>
+          <t>201368</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>175288</t>
+          <t>193231</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>188896</t>
+          <t>207561</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>698971</t>
+          <t>502109</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>670550</t>
+          <t>487233</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>728784</t>
+          <t>513410</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>6514</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>2358</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17537</t>
+          <t>13994</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13721</t>
+          <t>12825</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>13227</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24026</t>
+          <t>22870</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>16192</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32021</t>
+          <t>26124</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7542</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13244</t>
+          <t>13705</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>21624</t>
+          <t>24015</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>16232</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37252</t>
+          <t>35086</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,22 +2385,22 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>587</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6694</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>8802</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>691</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>8229</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7819</t>
+          <t>9009</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>118498</t>
+          <t>127826</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>108300</t>
+          <t>116817</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125838</t>
+          <t>134969</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,17 +2802,17 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>76567</t>
+          <t>84028</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70781</t>
+          <t>77718</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80472</t>
+          <t>88506</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>195065</t>
+          <t>211855</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>184693</t>
+          <t>199783</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>204120</t>
+          <t>221481</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,67%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>12980</t>
+          <t>13684</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23970</t>
+          <t>24814</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>6244</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,17 +2950,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>16352</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25456</t>
+          <t>27275</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -2993,32 +2993,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10355</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3063,32 +3063,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>12679</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18174</t>
+          <t>16840</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>10457</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15113</t>
+          <t>17001</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>20802</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8760</t>
+          <t>14239</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28087</t>
+          <t>29421</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>10489</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>12151</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>9449</t>
+          <t>10674</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>18983</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -3336,67 +3336,67 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>6678</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>7237</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>2318</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>772</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8987</t>
+          <t>10427</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11287</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16944</t>
+          <t>18988</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>783966</t>
+          <t>587732</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>751539</t>
+          <t>570074</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>821625</t>
+          <t>602400</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>301473</t>
+          <t>329630</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>291390</t>
+          <t>319875</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>309803</t>
+          <t>337576</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1085439</t>
+          <t>917362</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1052678</t>
+          <t>897617</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1129955</t>
+          <t>934561</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>14560</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40113</t>
+          <t>35762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>10944</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17747</t>
+          <t>17489</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>33651</t>
+          <t>35374</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14808</t>
+          <t>24776</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>50348</t>
+          <t>50643</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -3788,32 +3788,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>24296</t>
+          <t>27705</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>18571</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40548</t>
+          <t>39138</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3823,32 +3823,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15565</t>
+          <t>16818</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3858,32 +3858,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>37593</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>17054</t>
+          <t>27192</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>49768</t>
+          <t>50743</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
